--- a/polls/020_voter_exit_poll_form_template--polls.xlsx
+++ b/polls/020_voter_exit_poll_form_template--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How much time do you spend on news consumption?</t>
+          <t>Voter Exit Poll Form Template Page 1 Question 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How do you describe your religious affiliation?</t>
+          <t>Voter Exit Poll Form Template Page 2 Question 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How much do you trust government to solve problems?</t>
+          <t>Voter Exit Poll Form Template Page 2 Question 7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How often do you participate in social media?</t>
+          <t>Voter Exit Poll Form Template Page 4 Question 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How often do you engage with politicians or political campaigns?</t>
+          <t>Voter Exit Poll Form Template Page 4 Question 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How often do you participate in online forums, comment sections or chat rooms?</t>
+          <t>Voter Exit Poll Form Template Page 4 Question 6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_1_question_2_choices</t>
+          <t>voter_exit_poll_form_template_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1216,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_2_choices</t>
+          <t>voter_exit_poll_form_template_page_2_question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_2_question_2_choices</t>
+          <t>voter_exit_poll_form_template_page_2_question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_2_question_3_choices</t>
+          <t>voter_exit_poll_form_template_page_2_question_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_2_question_4_choices</t>
+          <t>voter_exit_poll_form_template_page_2_question_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_2_question_5_choices</t>
+          <t>voter_exit_poll_form_template_page_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_3_choices</t>
+          <t>voter_exit_poll_form_template_page_3_question_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_3_question_2_choices</t>
+          <t>voter_exit_poll_form_template_page_3_question_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_3_question_3_choices</t>
+          <t>voter_exit_poll_form_template_page_4_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_4_choices</t>
+          <t>voter_exit_poll_form_template_page_4_question_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>voter_exit_poll_form_template_page_4_question_3_choices</t>
+          <t>voter_exit_poll_form_template_page_4_question_5_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1556,27 +1556,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>voter_exit_poll_form_template_page_4_question_5_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
